--- a/backend/storage/schema/quotation_template.xlsx
+++ b/backend/storage/schema/quotation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3133C9E8-F336-7E4F-86B8-05399630F615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C856886F-C3B1-204E-8553-32BFADAC1628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6260" yWindow="3100" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="231">
   <si>
     <t>field_name</t>
   </si>
@@ -61,9 +61,6 @@
     <t>text</t>
   </si>
   <si>
-    <t>select</t>
-  </si>
-  <si>
     <t>iquote_link</t>
   </si>
   <si>
@@ -388,12 +385,6 @@
     <t>db:provinces</t>
   </si>
   <si>
-    <t>sample_size</t>
-  </si>
-  <si>
-    <t>Sample Size</t>
-  </si>
-  <si>
     <t>Province</t>
   </si>
   <si>
@@ -623,6 +614,123 @@
   </si>
   <si>
     <t>Số ngày sử dụng mỗi sản phẩm</t>
+  </si>
+  <si>
+    <t>CLT,HUT</t>
+  </si>
+  <si>
+    <t>F2F,CLT,HUT</t>
+  </si>
+  <si>
+    <t>tablet_usage_duration</t>
+  </si>
+  <si>
+    <t>Thiết bị phỏng vấn</t>
+  </si>
+  <si>
+    <t>excel:device_types</t>
+  </si>
+  <si>
+    <t>device_types</t>
+  </si>
+  <si>
+    <t>Tablet &gt;= 9 inch</t>
+  </si>
+  <si>
+    <t>Tablet &lt; 9 inch</t>
+  </si>
+  <si>
+    <t>Không yêu cầu</t>
+  </si>
+  <si>
+    <t>pm_required</t>
+  </si>
+  <si>
+    <t>Có yêu cầu PM không</t>
+  </si>
+  <si>
+    <t>excel:yes_no_question</t>
+  </si>
+  <si>
+    <t>Yêu cầu timing</t>
+  </si>
+  <si>
+    <t>timing_required</t>
+  </si>
+  <si>
+    <t>pilot_required</t>
+  </si>
+  <si>
+    <t>pilot_required_config</t>
+  </si>
+  <si>
+    <t>number_of_pilots</t>
+  </si>
+  <si>
+    <t>pilot_provinces</t>
+  </si>
+  <si>
+    <t>Thành phố thực hiện</t>
+  </si>
+  <si>
+    <t>pilot_comment</t>
+  </si>
+  <si>
+    <t>observe_required</t>
+  </si>
+  <si>
+    <t>Yêu cầu Observe</t>
+  </si>
+  <si>
+    <t>Yêu cầu Pilot</t>
+  </si>
+  <si>
+    <t>observe_required_config</t>
+  </si>
+  <si>
+    <t>number_of_observes</t>
+  </si>
+  <si>
+    <t>observe_provinces</t>
+  </si>
+  <si>
+    <t>observe_comment</t>
+  </si>
+  <si>
+    <t>Số lượng bài pilot</t>
+  </si>
+  <si>
+    <t>cost_required</t>
+  </si>
+  <si>
+    <t>Yêu cầu Cost</t>
+  </si>
+  <si>
+    <t>cost_required_config</t>
+  </si>
+  <si>
+    <t>cost_cpi</t>
+  </si>
+  <si>
+    <t>Tách CPI theo…</t>
+  </si>
+  <si>
+    <t>cost_projects</t>
+  </si>
+  <si>
+    <t>So sánh cost dự án/ báo giá cũ</t>
+  </si>
+  <si>
+    <t>sample_size_main</t>
+  </si>
+  <si>
+    <t>sample_size_booster</t>
+  </si>
+  <si>
+    <t>Sample Size Main</t>
+  </si>
+  <si>
+    <t>Sample Size Booster</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6694FA44-4A7D-4629-A892-7DFDEEB80386}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -1031,30 +1139,30 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -1075,7 +1183,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -1092,10 +1200,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -1115,10 +1223,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -1137,10 +1245,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
@@ -1157,10 +1265,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -1177,19 +1285,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H8">
         <v>12</v>
@@ -1197,13 +1305,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1214,19 +1322,19 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H10">
         <v>12</v>
@@ -1234,19 +1342,19 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H11">
         <v>12</v>
@@ -1254,19 +1362,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
         <v>80</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>81</v>
       </c>
       <c r="H12">
         <v>12</v>
@@ -1274,19 +1382,19 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
         <v>63</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -1294,19 +1402,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
         <v>113</v>
-      </c>
-      <c r="B14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>114</v>
       </c>
       <c r="H14">
         <v>12</v>
@@ -1314,19 +1422,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H15">
         <v>12</v>
@@ -1334,46 +1442,140 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="H16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C20" s="1"/>
+        <v>146</v>
+      </c>
+      <c r="H17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" t="s">
+        <v>221</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>222</v>
+      </c>
+      <c r="H20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>207</v>
+      </c>
+      <c r="H21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>212</v>
+      </c>
+      <c r="B22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>215</v>
+      </c>
+      <c r="H22">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1383,20 +1585,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8FC54-75D4-4AC2-B92C-338AB72929A6}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1411,606 +1614,898 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" t="s">
         <v>183</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C9" t="s">
         <v>187</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" t="s">
         <v>189</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="D12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
         <v>81</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
         <v>82</v>
       </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="H13" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="D15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
         <v>85</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="H16" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
         <v>91</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C18" t="s">
         <v>93</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="H18" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
         <v>104</v>
       </c>
-      <c r="C18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="D19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
         <v>102</v>
       </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="D20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
         <v>109</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="C22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
         <v>114</v>
       </c>
-      <c r="B21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="H22" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="B25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>120</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>154</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B35" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" t="s">
+        <v>224</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" t="s">
+        <v>226</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
         <v>114</v>
       </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="H37" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" t="s">
+        <v>217</v>
+      </c>
+      <c r="C40" t="s">
+        <v>210</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
         <v>114</v>
       </c>
-      <c r="B23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>121</v>
-      </c>
-      <c r="B24" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" t="s">
-        <v>144</v>
-      </c>
-      <c r="C26" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C27" t="s">
-        <v>141</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>136</v>
-      </c>
-      <c r="B28" t="s">
-        <v>145</v>
-      </c>
-      <c r="C28" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>136</v>
-      </c>
-      <c r="B29" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" t="s">
-        <v>143</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>149</v>
-      </c>
-      <c r="B30" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="G30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>149</v>
-      </c>
-      <c r="B31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" t="s">
-        <v>153</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>149</v>
-      </c>
-      <c r="B33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" t="s">
-        <v>156</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
+      <c r="H40" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C41" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" t="s">
+        <v>218</v>
+      </c>
+      <c r="C42" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2020,7 +2515,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256469AD-8C25-494B-B7FC-7D7B2DDE1DC0}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -2030,10 +2525,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
         <v>30</v>
-      </c>
-      <c r="B1" t="s">
-        <v>31</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -2041,530 +2536,574 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
         <v>46</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
         <v>52</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B27">
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B30">
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B43">
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B48">
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B49">
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>177</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50">
+        <v>9999</v>
+      </c>
+      <c r="C50" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>197</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53">
+        <v>3</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/backend/storage/schema/quotation_template.xlsx
+++ b/backend/storage/schema/quotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C91926-6C16-9B43-B318-2472916B500B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8F7874-B1A2-EB40-B42F-64DBF02585B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5740" yWindow="3680" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
+    <workbookView xWindow="5740" yWindow="3680" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FIELDS" sheetId="1" r:id="rId1"/>
@@ -571,9 +571,6 @@
     <t>CLT,HUT</t>
   </si>
   <si>
-    <t>F2F,CLT,HUT</t>
-  </si>
-  <si>
     <t>tablet_usage_duration</t>
   </si>
   <si>
@@ -1007,6 +1004,9 @@
   </si>
   <si>
     <t>Quota sampling</t>
+  </si>
+  <si>
+    <t>F2F,CLT,HUT,CATI</t>
   </si>
 </sst>
 </file>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" t="s">
         <v>294</v>
-      </c>
-      <c r="B2" t="s">
-        <v>295</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>77</v>
@@ -1458,22 +1458,22 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2">
         <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B3" t="s">
         <v>313</v>
-      </c>
-      <c r="B3" t="s">
-        <v>314</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>77</v>
@@ -1482,13 +1482,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H3">
         <v>12</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1496,7 +1496,7 @@
         <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>77</v>
@@ -1511,7 +1511,7 @@
         <v>12</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1534,7 +1534,7 @@
         <v>12</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1557,15 +1557,15 @@
         <v>12</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" t="s">
         <v>261</v>
-      </c>
-      <c r="B7" t="s">
-        <v>262</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>77</v>
@@ -1574,13 +1574,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H7">
         <v>12</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1603,15 +1603,15 @@
         <v>12</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" t="s">
         <v>215</v>
-      </c>
-      <c r="B9" t="s">
-        <v>216</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>77</v>
@@ -1620,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H9">
         <v>12</v>
@@ -1649,7 +1649,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -1672,7 +1672,7 @@
         <v>12</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1695,15 +1695,15 @@
         <v>12</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>52</v>
@@ -1715,15 +1715,15 @@
         <v>12</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B14" t="s">
         <v>184</v>
-      </c>
-      <c r="B14" t="s">
-        <v>185</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>19</v>
@@ -1732,21 +1732,21 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H14">
         <v>12</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" t="s">
         <v>203</v>
-      </c>
-      <c r="B15" t="s">
-        <v>204</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>77</v>
@@ -1755,21 +1755,21 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H15">
         <v>12</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>24</v>
@@ -1778,21 +1778,21 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H16">
         <v>12</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" t="s">
         <v>195</v>
-      </c>
-      <c r="B17" t="s">
-        <v>196</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>24</v>
@@ -1801,21 +1801,21 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H17">
         <v>12</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B18" t="s">
         <v>265</v>
-      </c>
-      <c r="B18" t="s">
-        <v>266</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>24</v>
@@ -1824,13 +1824,13 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H18">
         <v>12</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -1865,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1885,16 +1885,16 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -1905,21 +1905,21 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
@@ -1930,21 +1930,21 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>6</v>
@@ -1955,21 +1955,21 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>6</v>
@@ -1980,12 +1980,12 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1994,7 +1994,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>6</v>
@@ -2005,12 +2005,12 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -2019,25 +2019,25 @@
         <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2046,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>52</v>
@@ -2057,75 +2057,75 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>54</v>
@@ -2135,10 +2135,10 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -2152,10 +2152,10 @@
         <v>15</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2164,7 +2164,7 @@
         <v>61</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -2172,13 +2172,13 @@
         <v>156</v>
       </c>
       <c r="B13" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" t="s">
         <v>317</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>23</v>
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -2201,7 +2201,7 @@
         <v>101</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>54</v>
@@ -2214,7 +2214,7 @@
         <v>62</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -2225,10 +2225,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>19</v>
@@ -2240,7 +2240,7 @@
         <v>60</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -2248,13 +2248,13 @@
         <v>156</v>
       </c>
       <c r="B16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" t="s">
         <v>178</v>
       </c>
-      <c r="C16" t="s">
-        <v>179</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>54</v>
@@ -2264,10 +2264,10 @@
       </c>
       <c r="G16" s="1"/>
       <c r="H16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -2291,7 +2291,7 @@
         <v>71</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -2350,7 +2350,7 @@
         <v>37</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -2359,7 +2359,7 @@
         <v>76</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -2379,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
@@ -2399,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -2407,10 +2407,10 @@
         <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>6</v>
@@ -2419,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
@@ -2433,7 +2433,7 @@
         <v>79</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2442,7 +2442,7 @@
         <v>80</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
@@ -2462,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -2470,10 +2470,10 @@
         <v>57</v>
       </c>
       <c r="B26" t="s">
+        <v>285</v>
+      </c>
+      <c r="C26" t="s">
         <v>286</v>
-      </c>
-      <c r="C26" t="s">
-        <v>287</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>6</v>
@@ -2482,12 +2482,12 @@
         <v>1</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s">
         <v>86</v>
@@ -2505,12 +2505,12 @@
         <v>88</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
@@ -2525,12 +2525,12 @@
         <v>1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s">
         <v>95</v>
@@ -2545,18 +2545,18 @@
         <v>1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>52</v>
@@ -2565,12 +2565,12 @@
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s">
         <v>102</v>
@@ -2585,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
@@ -2599,7 +2599,7 @@
         <v>109</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2608,7 +2608,7 @@
         <v>108</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -2616,22 +2616,22 @@
         <v>107</v>
       </c>
       <c r="B33" t="s">
+        <v>267</v>
+      </c>
+      <c r="C33" t="s">
         <v>268</v>
       </c>
-      <c r="C33" t="s">
+      <c r="E33" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
         <v>269</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
-        <v>270</v>
-      </c>
       <c r="I33" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
@@ -2639,19 +2639,19 @@
         <v>107</v>
       </c>
       <c r="B34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
@@ -2659,10 +2659,10 @@
         <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>23</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
@@ -2682,10 +2682,10 @@
         <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>23</v>
@@ -2697,12 +2697,12 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s">
         <v>164</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
         <v>165</v>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
         <v>168</v>
@@ -2765,7 +2765,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s">
         <v>169</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s">
         <v>174</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s">
+        <v>216</v>
+      </c>
+      <c r="C42" t="s">
         <v>217</v>
-      </c>
-      <c r="C42" t="s">
-        <v>218</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>52</v>
@@ -2828,13 +2828,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s">
+        <v>237</v>
+      </c>
+      <c r="C43" t="s">
         <v>238</v>
-      </c>
-      <c r="C43" t="s">
-        <v>239</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>19</v>
@@ -2852,13 +2852,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s">
+        <v>239</v>
+      </c>
+      <c r="C44" t="s">
         <v>240</v>
-      </c>
-      <c r="C44" t="s">
-        <v>241</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>19</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="G44" s="1"/>
       <c r="H44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>176</v>
@@ -2876,13 +2876,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>54</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G45" s="1"/>
       <c r="H45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>176</v>
@@ -2900,13 +2900,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>52</v>
@@ -2921,13 +2921,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" t="s">
         <v>226</v>
-      </c>
-      <c r="C47" t="s">
-        <v>227</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>52</v>
@@ -2942,13 +2942,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>19</v>
@@ -2966,13 +2966,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C49" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>52</v>
@@ -2987,13 +2987,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B50" t="s">
+        <v>230</v>
+      </c>
+      <c r="C50" t="s">
         <v>231</v>
-      </c>
-      <c r="C50" t="s">
-        <v>232</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>52</v>
@@ -3008,13 +3008,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>19</v>
@@ -3032,13 +3032,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C52" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>19</v>
@@ -3065,7 +3065,7 @@
         <v>113</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         <v>114</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
@@ -3097,7 +3097,7 @@
         <v>121</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
@@ -3105,10 +3105,10 @@
         <v>112</v>
       </c>
       <c r="B55" t="s">
+        <v>258</v>
+      </c>
+      <c r="C55" t="s">
         <v>259</v>
-      </c>
-      <c r="C55" t="s">
-        <v>260</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>52</v>
@@ -3117,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
@@ -3137,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
@@ -3157,7 +3157,7 @@
         <v>1</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
@@ -3177,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
@@ -3197,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
@@ -3220,7 +3220,7 @@
         <v>46</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
@@ -3243,7 +3243,7 @@
         <v>46</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
@@ -3266,7 +3266,7 @@
         <v>148</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
@@ -3286,18 +3286,18 @@
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>204</v>
+      </c>
+      <c r="B64" t="s">
         <v>205</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>206</v>
-      </c>
-      <c r="C64" t="s">
-        <v>207</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>52</v>
@@ -3306,18 +3306,18 @@
         <v>1</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B65" t="s">
+        <v>207</v>
+      </c>
+      <c r="C65" t="s">
         <v>208</v>
-      </c>
-      <c r="C65" t="s">
-        <v>209</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>52</v>
@@ -3326,21 +3326,21 @@
         <v>1</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B66" t="s">
+        <v>191</v>
+      </c>
+      <c r="C66" t="s">
         <v>192</v>
       </c>
-      <c r="C66" t="s">
-        <v>193</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -3349,18 +3349,18 @@
         <v>108</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="s">
         <v>190</v>
       </c>
-      <c r="B67" t="s">
-        <v>191</v>
-      </c>
       <c r="C67" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>23</v>
@@ -3369,15 +3369,15 @@
         <v>1</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B68" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C68" t="s">
         <v>173</v>
@@ -3389,21 +3389,21 @@
         <v>1</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B69" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C69" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -3412,18 +3412,18 @@
         <v>108</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>197</v>
+      </c>
+      <c r="B70" t="s">
         <v>198</v>
       </c>
-      <c r="B70" t="s">
-        <v>199</v>
-      </c>
       <c r="C70" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>23</v>
@@ -3432,15 +3432,15 @@
         <v>1</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B71" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C71" t="s">
         <v>173</v>
@@ -3452,12 +3452,12 @@
         <v>1</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B72" t="s">
         <v>104</v>
@@ -3466,7 +3466,7 @@
         <v>109</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -3475,38 +3475,38 @@
         <v>108</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>266</v>
+      </c>
+      <c r="B73" t="s">
         <v>267</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>268</v>
       </c>
-      <c r="C73" t="s">
+      <c r="E73" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
         <v>269</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-      <c r="H73" t="s">
-        <v>270</v>
-      </c>
       <c r="I73" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B74" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C74" t="s">
         <v>173</v>
@@ -3518,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -3630,7 +3630,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -3696,10 +3696,10 @@
         <v>75</v>
       </c>
       <c r="B15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" t="s">
         <v>245</v>
-      </c>
-      <c r="C15" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3707,10 +3707,10 @@
         <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3718,10 +3718,10 @@
         <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -3729,10 +3729,10 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3740,10 +3740,10 @@
         <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3751,10 +3751,10 @@
         <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3762,10 +3762,10 @@
         <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3798,7 +3798,7 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3809,7 +3809,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -4122,29 +4122,29 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>180</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
         <v>181</v>
-      </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B56">
         <v>3</v>
@@ -4155,40 +4155,40 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -4199,7 +4199,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B61">
         <v>3</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -4221,112 +4221,112 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>270</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
         <v>271</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>303</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
         <v>304</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
-      </c>
-      <c r="C66" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B68">
         <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B69">
         <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B70">
         <v>5</v>
       </c>
       <c r="C70" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B71">
         <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B72">
         <v>7</v>
       </c>
       <c r="C72" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
